--- a/Team-Data/2012-13/12-4-2012-13.xlsx
+++ b/Team-Data/2012-13/12-4-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
         <v>10</v>
@@ -751,13 +818,13 @@
         <v>8</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
         <v>8</v>
@@ -769,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
         <v>30</v>
@@ -781,13 +848,13 @@
         <v>28</v>
       </c>
       <c r="AR2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS2" t="n">
         <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU2" t="n">
         <v>3</v>
@@ -799,7 +866,7 @@
         <v>3</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -808,10 +875,10 @@
         <v>2</v>
       </c>
       <c r="BA2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
         <v>9</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -921,19 +988,19 @@
         <v>-0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
         <v>10</v>
       </c>
       <c r="AF3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI3" t="n">
         <v>14</v>
@@ -951,13 +1018,13 @@
         <v>29</v>
       </c>
       <c r="AN3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
         <v>3</v>
@@ -975,7 +1042,7 @@
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
         <v>14</v>
@@ -990,7 +1057,7 @@
         <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
         <v>15</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -1025,115 +1092,115 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
         <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.647</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>48.3</v>
       </c>
       <c r="I4" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J4" t="n">
-        <v>81.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="M4" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.342</v>
+        <v>0.335</v>
       </c>
       <c r="O4" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P4" t="n">
         <v>23.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.725</v>
+        <v>0.719</v>
       </c>
       <c r="R4" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="S4" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="T4" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U4" t="n">
         <v>21.6</v>
       </c>
       <c r="V4" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="W4" t="n">
         <v>6.9</v>
       </c>
       <c r="X4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.2</v>
+        <v>95.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>6</v>
       </c>
       <c r="AF4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG4" t="n">
         <v>6</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
         <v>18</v>
@@ -1142,19 +1209,19 @@
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS4" t="n">
         <v>26</v>
       </c>
       <c r="AT4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV4" t="n">
         <v>4</v>
@@ -1163,19 +1230,19 @@
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>7</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -1285,10 +1352,10 @@
         <v>-5.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
         <v>16</v>
@@ -1303,7 +1370,7 @@
         <v>26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK5" t="n">
         <v>28</v>
@@ -1312,13 +1379,13 @@
         <v>17</v>
       </c>
       <c r="AM5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP5" t="n">
         <v>5</v>
@@ -1330,10 +1397,10 @@
         <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU5" t="n">
         <v>29</v>
@@ -1357,7 +1424,7 @@
         <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC5" t="n">
         <v>28</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>35.3</v>
+        <v>35.8</v>
       </c>
       <c r="J6" t="n">
-        <v>80.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.438</v>
+        <v>0.441</v>
       </c>
       <c r="L6" t="n">
         <v>3.9</v>
@@ -1419,76 +1486,76 @@
         <v>12.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.321</v>
+        <v>0.32</v>
       </c>
       <c r="O6" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P6" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="Q6" t="n">
         <v>0.789</v>
       </c>
       <c r="R6" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S6" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T6" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="U6" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="V6" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="W6" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA6" t="n">
         <v>21.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI6" t="n">
         <v>20</v>
       </c>
-      <c r="AE6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>24</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1503,7 +1570,7 @@
         <v>7</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
         <v>5</v>
@@ -1518,28 +1585,28 @@
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW6" t="n">
         <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
         <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
@@ -1661,10 +1728,10 @@
         <v>28</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ7" t="n">
         <v>3</v>
@@ -1679,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
         <v>19</v>
@@ -1688,7 +1755,7 @@
         <v>19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR7" t="n">
         <v>2</v>
@@ -1697,13 +1764,13 @@
         <v>28</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW7" t="n">
         <v>8</v>
@@ -1715,13 +1782,13 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="n">
         <v>18</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -1831,22 +1898,22 @@
         <v>-1.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF8" t="n">
         <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ8" t="n">
         <v>15</v>
@@ -1858,7 +1925,7 @@
         <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN8" t="n">
         <v>4</v>
@@ -1876,10 +1943,10 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>11</v>
@@ -1888,13 +1955,13 @@
         <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
         <v>25</v>
@@ -1903,10 +1970,10 @@
         <v>17</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>10</v>
@@ -2025,7 +2092,7 @@
         <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
         <v>3</v>
@@ -2037,10 +2104,10 @@
         <v>9</v>
       </c>
       <c r="AL9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN9" t="n">
         <v>25</v>
@@ -2049,7 +2116,7 @@
         <v>20</v>
       </c>
       <c r="AP9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
         <v>29</v>
@@ -2067,28 +2134,28 @@
         <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY9" t="n">
         <v>25</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
         <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -2216,16 +2283,16 @@
         <v>24</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
         <v>26</v>
       </c>
       <c r="AM10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
         <v>15</v>
@@ -2240,10 +2307,10 @@
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU10" t="n">
         <v>20</v>
@@ -2255,13 +2322,13 @@
         <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
         <v>11</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2401,16 +2468,16 @@
         <v>10</v>
       </c>
       <c r="AL11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN11" t="n">
         <v>19</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>15</v>
@@ -2446,7 +2513,7 @@
         <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -2481,106 +2548,106 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.529</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
         <v>48.6</v>
       </c>
       <c r="I12" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J12" t="n">
-        <v>85.2</v>
+        <v>84.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.439</v>
+        <v>0.443</v>
       </c>
       <c r="L12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>26.4</v>
+        <v>25.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.348</v>
+        <v>0.36</v>
       </c>
       <c r="O12" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="P12" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="Q12" t="n">
         <v>0.773</v>
       </c>
       <c r="R12" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="S12" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="T12" t="n">
-        <v>45.2</v>
+        <v>44.9</v>
       </c>
       <c r="U12" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16.3</v>
+        <v>16.7</v>
       </c>
       <c r="W12" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.7</v>
+        <v>19.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.7</v>
+        <v>103.5</v>
       </c>
       <c r="AC12" t="n">
         <v>1.1</v>
       </c>
       <c r="AD12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG12" t="n">
         <v>13</v>
       </c>
-      <c r="AE12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>11</v>
-      </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AI12" t="n">
         <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AL12" t="n">
         <v>2</v>
@@ -2589,10 +2656,10 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP12" t="n">
         <v>4</v>
@@ -2601,10 +2668,10 @@
         <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>6</v>
@@ -2613,22 +2680,22 @@
         <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AW12" t="n">
         <v>7</v>
       </c>
       <c r="AX12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY12" t="n">
         <v>26</v>
       </c>
-      <c r="AY12" t="n">
-        <v>27</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB12" t="n">
         <v>3</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -2663,112 +2730,112 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
         <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="H13" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I13" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="J13" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.411</v>
+        <v>0.414</v>
       </c>
       <c r="L13" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="M13" t="n">
-        <v>19.4</v>
+        <v>19.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.327</v>
+        <v>0.33</v>
       </c>
       <c r="O13" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P13" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.725</v>
+        <v>0.724</v>
       </c>
       <c r="R13" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="S13" t="n">
-        <v>34.3</v>
+        <v>34.5</v>
       </c>
       <c r="T13" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V13" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="X13" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA13" t="n">
         <v>21.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>90.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AF13" t="n">
         <v>16</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AN13" t="n">
         <v>26</v>
@@ -2777,13 +2844,13 @@
         <v>17</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AQ13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS13" t="n">
         <v>1</v>
@@ -2792,19 +2859,19 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ13" t="n">
         <v>8</v>
@@ -2813,10 +2880,10 @@
         <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -2923,43 +2990,43 @@
         <v>5.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
       </c>
       <c r="AF14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG14" t="n">
         <v>7</v>
       </c>
-      <c r="AG14" t="n">
-        <v>6</v>
-      </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
       </c>
       <c r="AL14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM14" t="n">
         <v>14</v>
       </c>
-      <c r="AM14" t="n">
-        <v>13</v>
-      </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
         <v>10</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
         <v>17</v>
@@ -2986,7 +3053,7 @@
         <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ14" t="n">
         <v>27</v>
@@ -2995,7 +3062,7 @@
         <v>8</v>
       </c>
       <c r="BB14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -3027,94 +3094,94 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
         <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.444</v>
+        <v>0.471</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J15" t="n">
-        <v>78.5</v>
+        <v>78.2</v>
       </c>
       <c r="K15" t="n">
         <v>0.457</v>
       </c>
       <c r="L15" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M15" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P15" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.664</v>
+        <v>0.665</v>
       </c>
       <c r="R15" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S15" t="n">
-        <v>33.3</v>
+        <v>33.1</v>
       </c>
       <c r="T15" t="n">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="U15" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="V15" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W15" t="n">
         <v>7.7</v>
       </c>
       <c r="X15" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF15" t="n">
         <v>16</v>
       </c>
-      <c r="AF15" t="n">
-        <v>20</v>
-      </c>
       <c r="AG15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3135,7 +3202,7 @@
         <v>6</v>
       </c>
       <c r="AN15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO15" t="n">
         <v>2</v>
@@ -3147,7 +3214,7 @@
         <v>30</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS15" t="n">
         <v>3</v>
@@ -3156,28 +3223,28 @@
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>30</v>
       </c>
       <c r="AW15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
         <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC15" t="n">
         <v>8</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -3209,85 +3276,85 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O16" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="P16" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0.8129999999999999</v>
       </c>
-      <c r="H16" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="L16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M16" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="O16" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="P16" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="R16" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S16" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="T16" t="n">
-        <v>42.3</v>
+        <v>41.8</v>
       </c>
       <c r="U16" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z16" t="n">
         <v>21.2</v>
       </c>
-      <c r="V16" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="X16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>21.3</v>
-      </c>
       <c r="AA16" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>99.3</v>
+        <v>98.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,31 +3366,31 @@
         <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ16" t="n">
         <v>10</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AM16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ16" t="n">
         <v>2</v>
@@ -3332,34 +3399,34 @@
         <v>9</v>
       </c>
       <c r="AS16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA16" t="n">
         <v>3</v>
       </c>
       <c r="BB16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC16" t="n">
         <v>3</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -3391,103 +3458,103 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J17" t="n">
-        <v>79.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.493</v>
+        <v>0.495</v>
       </c>
       <c r="L17" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.413</v>
+        <v>0.425</v>
       </c>
       <c r="O17" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="P17" t="n">
-        <v>22.9</v>
+        <v>23.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.757</v>
+        <v>0.761</v>
       </c>
       <c r="R17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="S17" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T17" t="n">
-        <v>39.4</v>
+        <v>39.1</v>
       </c>
       <c r="U17" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="V17" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W17" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z17" t="n">
         <v>19.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.4</v>
+        <v>104.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
         <v>1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK17" t="n">
         <v>1</v>
@@ -3496,19 +3563,19 @@
         <v>3</v>
       </c>
       <c r="AM17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AN17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3517,7 +3584,7 @@
         <v>12</v>
       </c>
       <c r="AT17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU17" t="n">
         <v>4</v>
@@ -3526,19 +3593,19 @@
         <v>5</v>
       </c>
       <c r="AW17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY17" t="n">
         <v>2</v>
       </c>
       <c r="AZ17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA17" t="n">
         <v>13</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>2</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3718,19 @@
         <v>-1.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
         <v>5</v>
@@ -3672,7 +3739,7 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL18" t="n">
         <v>25</v>
@@ -3696,19 +3763,19 @@
         <v>16</v>
       </c>
       <c r="AS18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT18" t="n">
         <v>17</v>
       </c>
       <c r="AU18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3717,13 +3784,13 @@
         <v>3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
         <v>27</v>
       </c>
       <c r="BB18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC18" t="n">
         <v>20</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -3755,100 +3822,100 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="H19" t="n">
         <v>48</v>
       </c>
       <c r="I19" t="n">
-        <v>34.1</v>
+        <v>33.6</v>
       </c>
       <c r="J19" t="n">
-        <v>79.8</v>
+        <v>80</v>
       </c>
       <c r="K19" t="n">
-        <v>0.427</v>
+        <v>0.42</v>
       </c>
       <c r="L19" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>19.3</v>
+        <v>18.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.305</v>
+        <v>0.286</v>
       </c>
       <c r="O19" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="P19" t="n">
-        <v>26.4</v>
+        <v>27.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.728</v>
+        <v>0.734</v>
       </c>
       <c r="R19" t="n">
-        <v>13.1</v>
+        <v>13.5</v>
       </c>
       <c r="S19" t="n">
-        <v>32.3</v>
+        <v>31.8</v>
       </c>
       <c r="T19" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="U19" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="V19" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W19" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X19" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.3</v>
+        <v>92.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="AD19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG19" t="n">
         <v>20</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>13</v>
       </c>
       <c r="AH19" t="n">
         <v>28</v>
       </c>
       <c r="AI19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ19" t="n">
         <v>23</v>
@@ -3857,58 +3924,58 @@
         <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AM19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AN19" t="n">
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
         <v>4</v>
       </c>
       <c r="AS19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
         <v>4</v>
       </c>
       <c r="AU19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
         <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
@@ -4027,7 +4094,7 @@
         <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI20" t="n">
         <v>26</v>
@@ -4039,7 +4106,7 @@
         <v>14</v>
       </c>
       <c r="AL20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM20" t="n">
         <v>21</v>
@@ -4051,7 +4118,7 @@
         <v>22</v>
       </c>
       <c r="AP20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ20" t="n">
         <v>4</v>
@@ -4072,7 +4139,7 @@
         <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX20" t="n">
         <v>18</v>
@@ -4087,7 +4154,7 @@
         <v>19</v>
       </c>
       <c r="BB20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC20" t="n">
         <v>26</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO21" t="n">
         <v>23</v>
@@ -4248,7 +4315,7 @@
         <v>26</v>
       </c>
       <c r="AU21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4266,7 +4333,7 @@
         <v>3</v>
       </c>
       <c r="BA21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB21" t="n">
         <v>4</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -4301,97 +4368,97 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="H22" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I22" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J22" t="n">
-        <v>76.2</v>
+        <v>76.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.492</v>
+        <v>0.486</v>
       </c>
       <c r="L22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M22" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="O22" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="R22" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="S22" t="n">
+        <v>33</v>
+      </c>
+      <c r="T22" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="U22" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="V22" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W22" t="n">
         <v>7.7</v>
       </c>
-      <c r="M22" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="O22" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.837</v>
-      </c>
-      <c r="R22" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="S22" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="T22" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="V22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>7.6</v>
-      </c>
       <c r="X22" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.7</v>
+        <v>105.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4406,10 +4473,10 @@
         <v>10</v>
       </c>
       <c r="AM22" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4421,22 +4488,22 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS22" t="n">
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4448,7 +4515,7 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -4561,37 +4628,37 @@
         <v>-3.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
         <v>23</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>12</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
       </c>
       <c r="AN23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4603,16 +4670,16 @@
         <v>6</v>
       </c>
       <c r="AR23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS23" t="n">
         <v>5</v>
       </c>
       <c r="AT23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV23" t="n">
         <v>13</v>
@@ -4621,7 +4688,7 @@
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -4665,100 +4732,100 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
         <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>0.556</v>
+        <v>0.588</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J24" t="n">
         <v>83</v>
       </c>
       <c r="K24" t="n">
-        <v>0.43</v>
+        <v>0.431</v>
       </c>
       <c r="L24" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="M24" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.374</v>
+        <v>0.382</v>
       </c>
       <c r="O24" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="P24" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.756</v>
+        <v>0.769</v>
       </c>
       <c r="R24" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="S24" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T24" t="n">
         <v>40.8</v>
       </c>
       <c r="U24" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V24" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X24" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="AA24" t="n">
         <v>17.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>-1.7</v>
+        <v>-0.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>8</v>
       </c>
       <c r="AF24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ24" t="n">
         <v>14</v>
@@ -4767,10 +4834,10 @@
         <v>24</v>
       </c>
       <c r="AL24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AN24" t="n">
         <v>6</v>
@@ -4782,19 +4849,19 @@
         <v>28</v>
       </c>
       <c r="AQ24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4803,22 +4870,22 @@
         <v>15</v>
       </c>
       <c r="AX24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BC24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -4847,97 +4914,97 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
         <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>0.368</v>
+        <v>0.389</v>
       </c>
       <c r="H25" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="I25" t="n">
         <v>38.5</v>
       </c>
       <c r="J25" t="n">
-        <v>85.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L25" t="n">
         <v>6.2</v>
       </c>
       <c r="M25" t="n">
-        <v>17.9</v>
+        <v>18.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.343</v>
+        <v>0.339</v>
       </c>
       <c r="O25" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="P25" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R25" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="S25" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="T25" t="n">
-        <v>40.8</v>
+        <v>41.3</v>
       </c>
       <c r="U25" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V25" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="W25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X25" t="n">
         <v>6.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB25" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-4.6</v>
+        <v>-4.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG25" t="n">
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AI25" t="n">
         <v>4</v>
@@ -4955,13 +5022,13 @@
         <v>24</v>
       </c>
       <c r="AN25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ25" t="n">
         <v>20</v>
@@ -4970,31 +5037,31 @@
         <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB25" t="n">
         <v>14</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -5107,19 +5174,19 @@
         <v>-3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI26" t="n">
         <v>17</v>
@@ -5137,13 +5204,13 @@
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO26" t="n">
         <v>14</v>
       </c>
       <c r="AP26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ26" t="n">
         <v>22</v>
@@ -5158,7 +5225,7 @@
         <v>24</v>
       </c>
       <c r="AU26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV26" t="n">
         <v>18</v>
@@ -5179,7 +5246,7 @@
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC26" t="n">
         <v>23</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>-6.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG27" t="n">
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI27" t="n">
         <v>18</v>
@@ -5319,7 +5386,7 @@
         <v>25</v>
       </c>
       <c r="AN27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
         <v>26</v>
@@ -5343,16 +5410,16 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
         <v>25</v>
       </c>
       <c r="AY27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5361,7 +5428,7 @@
         <v>28</v>
       </c>
       <c r="BB27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -5471,19 +5538,19 @@
         <v>6.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG28" t="n">
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO28" t="n">
         <v>21</v>
@@ -5516,7 +5583,7 @@
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
         <v>18</v>
@@ -5528,10 +5595,10 @@
         <v>16</v>
       </c>
       <c r="AW28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB28" t="n">
         <v>5</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-4.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>27</v>
@@ -5665,28 +5732,28 @@
         <v>28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI29" t="n">
         <v>19</v>
       </c>
       <c r="AJ29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK29" t="n">
         <v>25</v>
       </c>
       <c r="AL29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO29" t="n">
         <v>12</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>11</v>
       </c>
       <c r="AP29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -5841,10 +5908,10 @@
         <v>10</v>
       </c>
       <c r="AF30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
         <v>8</v>
@@ -5862,7 +5929,7 @@
         <v>16</v>
       </c>
       <c r="AM30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN30" t="n">
         <v>9</v>
@@ -5871,10 +5938,10 @@
         <v>8</v>
       </c>
       <c r="AP30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>3</v>
@@ -5904,13 +5971,13 @@
         <v>26</v>
       </c>
       <c r="BA30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB30" t="n">
         <v>9</v>
       </c>
       <c r="BC30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
@@ -5939,82 +6006,82 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>13</v>
       </c>
       <c r="G31" t="n">
-        <v>0.133</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="I31" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="J31" t="n">
-        <v>83.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.408</v>
+        <v>0.403</v>
       </c>
       <c r="L31" t="n">
         <v>6.6</v>
       </c>
       <c r="M31" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.306</v>
+        <v>0.302</v>
       </c>
       <c r="O31" t="n">
-        <v>15.4</v>
+        <v>14.9</v>
       </c>
       <c r="P31" t="n">
-        <v>20.5</v>
+        <v>19.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R31" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="S31" t="n">
-        <v>30.7</v>
+        <v>30.3</v>
       </c>
       <c r="T31" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U31" t="n">
-        <v>20.5</v>
+        <v>19.8</v>
       </c>
       <c r="V31" t="n">
-        <v>15.9</v>
+        <v>16.2</v>
       </c>
       <c r="W31" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="AA31" t="n">
         <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>90.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.5</v>
+        <v>-8.4</v>
       </c>
       <c r="AD31" t="n">
         <v>29</v>
@@ -6029,67 +6096,67 @@
         <v>30</v>
       </c>
       <c r="AH31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="n">
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
       </c>
       <c r="AL31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AN31" t="n">
         <v>29</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
         <v>18</v>
       </c>
       <c r="AR31" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AS31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AT31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW31" t="n">
         <v>9</v>
       </c>
-      <c r="AU31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>10</v>
-      </c>
       <c r="AX31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY31" t="n">
         <v>12</v>
       </c>
       <c r="AZ31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC31" t="n">
         <v>30</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-4-2012-13</t>
+          <t>2012-12-04</t>
         </is>
       </c>
     </row>
